--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCION 94/LTAIPT_A94F1.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCION 94/LTAIPT_A94F1.xlsx
@@ -226,28 +226,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>DF7CA536C89E24EC6129A3546EAAE3B0</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>11/07/2022</t>
-  </si>
-  <si>
-    <t>En el periodo del 01 de abril del 2022 al 30 de junio del 2022, el Colegio de Bachilleres del Estado de Tlaxcala no realizó ningún procedimiento de reserva de información pública.</t>
+    <t>31F0A383CADD26DA190A7251DF9116F2</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>Área de Transparencia</t>
+  </si>
+  <si>
+    <t>10/07/2023</t>
+  </si>
+  <si>
+    <t>Del 01 de enero del 2023 al 30 de junio del 2023, el Colegio de Bachilleres del Estado de Tlaxcala, no genero índices de los expedientes clasificados como reservados, por área responsable de la información y tema.</t>
   </si>
 </sst>
 </file>
@@ -643,7 +643,7 @@
   <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -672,7 +672,7 @@
     <col min="27" max="27" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="157.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="180.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="8" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>73</v>
@@ -1027,70 +1027,70 @@
         <v>74</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AA8" s="2" t="s">
         <v>75</v>
